--- a/giro_da_praça_ofertas - SEGUNDA - QUARTA - DE TERÇA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA - QUARTA - DE TERÇA.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F35EDE3-5A7E-4F85-89C3-9EB213FE5102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05A4DFE-4F45-4678-9F0B-85E25055F333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="98">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -232,6 +218,9 @@
   </si>
   <si>
     <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
+  </si>
+  <si>
+    <t>CAPIM LIMÃO, CLEAR, CLEAR CARE, COCO, LIMAO, MACA, NEUTRO</t>
   </si>
   <si>
     <t>#03 LIMPEZA - LIMPA ALUMINIO</t>
@@ -777,12 +766,11 @@
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="12" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1188,21 +1176,21 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="7">
         <v>130920</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="10">
-        <v>5.04</v>
+      <c r="E24" s="8"/>
+      <c r="F24" s="12">
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1328,7 +1316,7 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="10">
-        <v>9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1512,20 +1500,22 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="3">
         <v>100391</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="12">
+      <c r="E43" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="10">
         <v>2.79</v>
       </c>
     </row>
@@ -1534,16 +1524,16 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C44" s="3">
         <v>118939</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F44" s="10">
         <v>3.99</v>
@@ -1554,13 +1544,13 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C45" s="3">
         <v>261360</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="10">
@@ -1572,13 +1562,13 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C46" s="3">
         <v>240402</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="10">
@@ -1590,16 +1580,16 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C47" s="3">
         <v>286199</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" s="10">
         <v>10.99</v>
@@ -1610,13 +1600,13 @@
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C48" s="3">
         <v>100373</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="10">
@@ -1628,13 +1618,13 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C50" s="3">
         <v>104406</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="10">
@@ -1646,13 +1636,13 @@
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C51" s="3">
         <v>104404</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="10">
@@ -1664,13 +1654,13 @@
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C52" s="3">
         <v>122984</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="10">
@@ -1678,21 +1668,21 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="3">
+      <c r="A53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="7">
         <v>102287</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="10">
-        <v>5.4</v>
+      <c r="D53" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="12">
+        <v>4.6900000000000004</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1700,13 +1690,13 @@
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C54" s="3">
         <v>102237</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="10">
@@ -1718,13 +1708,13 @@
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C55" s="3">
         <v>267604</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="10">
@@ -1736,13 +1726,13 @@
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C56" s="3">
         <v>184034</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="10">
@@ -1750,58 +1740,58 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C57" s="3">
+      <c r="A57" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="7">
         <v>239446</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="10">
+      <c r="D57" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="12">
         <f>12*3.09</f>
         <v>37.08</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" s="3">
+      <c r="A58" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="7">
         <v>170451</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="10">
+      <c r="D58" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="12">
         <f>15*3.09</f>
         <v>46.349999999999994</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="3">
+      <c r="A59" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="7">
         <v>313599</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="10">
+      <c r="D59" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="12">
         <f>15*3.69</f>
         <v>55.35</v>
       </c>
@@ -1811,13 +1801,13 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="3">
         <v>102242</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="10">
@@ -1829,13 +1819,13 @@
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C61" s="3">
         <v>109729</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="10">
@@ -1847,13 +1837,13 @@
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C62" s="3">
         <v>244831</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="10">
@@ -1865,13 +1855,13 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C63" s="3">
         <v>102036</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="10">
